--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_377_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_377_R38.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3073</v>
+        <v>8.9306</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8392</v>
+        <v>7.4289</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4681</v>
+        <v>1.5017</v>
       </c>
       <c r="G2" t="n">
         <v>6.502</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4835</v>
+        <v>-0.8601</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5816</v>
+        <v>0.0081</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9019</v>
+        <v>-0.8683</v>
       </c>
       <c r="V2" t="n">
         <v>3.7527</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8576</v>
+        <v>4.3921</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3124</v>
+        <v>3.0149</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5452</v>
+        <v>1.3772</v>
       </c>
       <c r="G3" t="n">
         <v>2.6605</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.661</v>
+        <v>0.1955</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9109</v>
+        <v>0.6135</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.25</v>
+        <v>-0.418</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.78</v>
+        <v>4.1235</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3688</v>
+        <v>3.4434</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4113</v>
+        <v>0.6801</v>
       </c>
       <c r="G4" t="n">
         <v>5.2323</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2204</v>
+        <v>-0.8768</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0553</v>
+        <v>0.13</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2757</v>
+        <v>-1.0069</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.282</v>
+        <v>3.8614</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6093</v>
+        <v>5.9199</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3273</v>
+        <v>-2.0585</v>
       </c>
       <c r="G5" t="n">
         <v>1.894</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.3801</v>
+        <v>-1.8007</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0455</v>
+        <v>-0.735</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3346</v>
+        <v>-1.0657</v>
       </c>
       <c r="V5" t="n">
         <v>2.1444</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.927</v>
+        <v>1.5914</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3646</v>
+        <v>1.0291</v>
       </c>
       <c r="F6" t="n">
         <v>0.5624</v>
@@ -922,10 +922,10 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1993</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8057</v>
+        <v>-0.1412</v>
       </c>
       <c r="U6" t="n">
         <v>-0.3936</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2036</v>
+        <v>-0.7077</v>
       </c>
       <c r="E7" t="n">
         <v>-1.4724</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2688</v>
+        <v>0.7647</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8324</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6778</v>
+        <v>0.1737</v>
       </c>
       <c r="T7" t="n">
         <v>0.5034</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1744</v>
+        <v>-0.3297</v>
       </c>
       <c r="V7" t="n">
         <v>0.6468</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6151</v>
+        <v>-1.4053</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6123</v>
+        <v>-0.3017</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0028</v>
+        <v>-1.1036</v>
       </c>
       <c r="G8" t="n">
         <v>1.0197</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1013</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5816</v>
+        <v>-0.2711</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6801</v>
+        <v>-2.7577</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7688</v>
+        <v>0.4896</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4489</v>
+        <v>-3.2473</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2839</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3241</v>
+        <v>-1.4016</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1142</v>
+        <v>-0.165</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4383</v>
+        <v>-1.2366</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>17.6551</v>
+        <v>18.0283</v>
       </c>
       <c r="E10" t="n">
-        <v>19.1784</v>
+        <v>19.5517</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5232</v>
+        <v>-1.5233</v>
       </c>
       <c r="G10" t="n">
         <v>18.8366</v>
@@ -1234,13 +1234,13 @@
         <v>12.7575</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.369899999999999</v>
+        <v>-5.9964</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4306000000000002</v>
+        <v>-0.05730000000000002</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.9394</v>
+        <v>-5.9393</v>
       </c>
       <c r="V10" t="n">
         <v>5.188099999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.403</v>
+        <v>7.5888</v>
       </c>
       <c r="E11" t="n">
-        <v>9.4316</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0287</v>
+        <v>-2.1967</v>
       </c>
       <c r="G11" t="n">
         <v>7.2034</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2718</v>
+        <v>1.4576</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3462</v>
+        <v>0.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9256</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6179</v>
+        <v>3.1068</v>
       </c>
       <c r="E12" t="n">
-        <v>5.7399</v>
+        <v>4.9143</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.122</v>
+        <v>-1.8074</v>
       </c>
       <c r="G12" t="n">
         <v>1.1921</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>1.498</v>
+        <v>0.9869</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6201</v>
+        <v>0.7945</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1221</v>
+        <v>0.1924</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0628</v>
+        <v>0.8098</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4682</v>
+        <v>1.1144</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4054</v>
+        <v>-0.3046</v>
       </c>
       <c r="G13" t="n">
         <v>0.2014</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3976</v>
+        <v>0.1445</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4876</v>
+        <v>0.1338</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.3103</v>
+        <v>-1.1258</v>
       </c>
       <c r="E14" t="n">
-        <v>1.592</v>
+        <v>1.4741</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9023</v>
+        <v>-2.5999</v>
       </c>
       <c r="G14" t="n">
         <v>-2.3558</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3317</v>
+        <v>0.5162</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9164</v>
+        <v>0.7984</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5847</v>
+        <v>-0.2822</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6778999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>K. EDWARDS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.5389</v>
+        <v>-2.9323</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.8537</v>
+        <v>-1.8829</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3149</v>
+        <v>-1.0494</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.4632</v>
+        <v>-2.1862</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.0953</v>
+        <v>-0.7575</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3679</v>
+        <v>-1.4287</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4077</v>
+        <v>-1.3212</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.5182</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1104</v>
+        <v>-0.6391</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0555</v>
+        <v>-0.8651</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5771</v>
+        <v>-0.0755</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4783</v>
+        <v>-0.7896</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1769</v>
+        <v>0.7205</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8941</v>
+        <v>0.4562</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2828</v>
+        <v>0.2642</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3247</v>
+        <v>-1.4665</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7886</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. EDWARDS</t>
+          <t>L. RANDOLPH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.9494</v>
+        <v>-2.9772</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0009</v>
+        <v>-2.6743</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9486</v>
+        <v>-0.3029</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1862</v>
+        <v>-1.842</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7575</v>
+        <v>-1.6447</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4287</v>
+        <v>-0.1973</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3212</v>
+        <v>-0.1977</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.897</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6391</v>
+        <v>0.6993</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8651</v>
+        <v>-1.6443</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0755</v>
+        <v>-0.7477</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7896</v>
+        <v>-0.8966</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7033</v>
+        <v>0.2566</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3383</v>
+        <v>-0.1571</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3651</v>
+        <v>0.4136</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4665</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.998</v>
+        <v>-3.5091</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5009</v>
+        <v>-3.3265</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4971</v>
+        <v>-0.1826</v>
       </c>
       <c r="G17" t="n">
         <v>-5.6715</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7458</v>
+        <v>1.2346</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8442</v>
+        <v>1.0185</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0984</v>
+        <v>0.2161</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. RANDOLPH</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7349</v>
+        <v>-3.5985</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.264</v>
+        <v>-3.623</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4709</v>
+        <v>0.0245</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.842</v>
+        <v>-3.4632</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6447</v>
+        <v>-3.0953</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1973</v>
+        <v>-0.3679</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1977</v>
+        <v>-1.4077</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.897</v>
+        <v>-1.5182</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6993</v>
+        <v>0.1104</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6443</v>
+        <v>-2.0555</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7477</v>
+        <v>-1.5771</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8966</v>
+        <v>-0.4783</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5012</v>
+        <v>2.1172</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7468</v>
+        <v>1.1248</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2456</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.3247</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.2287</v>
+        <v>-3.6845</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7175</v>
+        <v>-0.6559</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5112</v>
+        <v>-3.0286</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8542</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3385</v>
+        <v>0.2056</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.507</v>
+        <v>0.5546</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8316</v>
+        <v>-0.349</v>
       </c>
       <c r="V19" t="n">
         <v>0.2836</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.9489</v>
+        <v>-4.6064</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8153</v>
+        <v>-3.7537</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1336</v>
+        <v>-0.8527</v>
       </c>
       <c r="G20" t="n">
         <v>-6.5915</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1075</v>
+        <v>0.235</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.963</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1445</v>
+        <v>0.1364</v>
       </c>
       <c r="V20" t="n">
         <v>1.7501</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0297</v>
+        <v>-5.154</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9505</v>
+        <v>-0.2428</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.0792</v>
+        <v>-4.9112</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4691</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8079</v>
+        <v>0.0679</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2908</v>
+        <v>0.4169</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5171</v>
+        <v>-0.349</v>
       </c>
       <c r="V21" t="n">
         <v>-2.6805</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-17.6551</v>
+        <v>-16.0824</v>
       </c>
       <c r="E22" t="n">
-        <v>1.128899999999996</v>
+        <v>1.1292</v>
       </c>
       <c r="F22" t="n">
-        <v>-18.7841</v>
+        <v>-17.2115</v>
       </c>
       <c r="G22" t="n">
         <v>-18.8366</v>
@@ -2170,13 +2170,13 @@
         <v>12.7575</v>
       </c>
       <c r="S22" t="n">
-        <v>6.370000000000001</v>
+        <v>7.9426</v>
       </c>
       <c r="T22" t="n">
-        <v>5.9393</v>
+        <v>5.9392</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4306000000000001</v>
+        <v>2.003299999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-5.1881</v>
